--- a/keelinjoyce/rowing/SLU Crew 2k Times.xlsx
+++ b/keelinjoyce/rowing/SLU Crew 2k Times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keelinjoyce/Desktop/SYE/github repos/stat450-spr2026-score/keelinjoyce/rowing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8FD9B51-E4D8-5348-8807-024C1A1B48BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA927B2-A3BF-5440-80F4-D07D02A8C680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13320" yWindow="840" windowWidth="15740" windowHeight="16760" xr2:uid="{2B2CA668-8B79-3A43-BD51-3E64AB62869C}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="29060" windowHeight="16760" xr2:uid="{2B2CA668-8B79-3A43-BD51-3E64AB62869C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,30 +125,15 @@
     <t>Nikolas Zocchi</t>
   </si>
   <si>
-    <t>Cam Kennedy</t>
+    <t>Cameron Kennedy</t>
   </si>
   <si>
     <t>Owen Strout</t>
   </si>
   <si>
-    <t>Will Sexton</t>
-  </si>
-  <si>
-    <t>Chris Augustine</t>
-  </si>
-  <si>
-    <t>Josh Malloy</t>
-  </si>
-  <si>
-    <t>Howie Mandell</t>
-  </si>
-  <si>
     <t>Austin Phelps</t>
   </si>
   <si>
-    <t>Joe Franenfeld</t>
-  </si>
-  <si>
     <t>Colby Englehart</t>
   </si>
   <si>
@@ -162,14 +147,37 @@
   </si>
   <si>
     <t>Kirby Oppenheimer</t>
+  </si>
+  <si>
+    <t>William Sexton</t>
+  </si>
+  <si>
+    <t>Christopher Augustine</t>
+  </si>
+  <si>
+    <t>Joshua Malloy</t>
+  </si>
+  <si>
+    <t>Howard Mandell</t>
+  </si>
+  <si>
+    <t>Josef Franenfeld</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -185,6 +193,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -209,16 +224,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="45" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="47" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="45" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,29 +557,29 @@
     <col min="8" max="8" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2466,7 +2483,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B75" s="2">
         <v>6.9444444444444434E-2</v>
@@ -2492,7 +2509,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B76" s="2">
         <v>6.9444444444444434E-2</v>
@@ -2518,7 +2535,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B77" s="2">
         <v>7.2916666666666671E-2</v>
@@ -2544,7 +2561,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B78" s="2">
         <v>7.3611111111111113E-2</v>
@@ -2570,7 +2587,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B79" s="2">
         <v>7.2916666666666671E-2</v>
@@ -2596,7 +2613,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B80" s="2">
         <v>7.5694444444444439E-2</v>
@@ -2622,7 +2639,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B81" s="2">
         <v>7.6388888888888895E-2</v>
@@ -2648,7 +2665,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B82" s="2">
         <v>7.6388888888888895E-2</v>
@@ -2778,7 +2795,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B87" s="7">
         <v>1.207175925925926E-3</v>
@@ -2804,7 +2821,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B88" s="7">
         <v>1.164351851851852E-3</v>
@@ -2830,7 +2847,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B89" s="7">
         <v>1.2280092592592592E-3</v>
@@ -2856,7 +2873,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B90" s="7">
         <v>1.2453703703703704E-3</v>
@@ -2882,7 +2899,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B91" s="7">
         <v>1.2430555555555556E-3</v>
@@ -2908,7 +2925,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B92" s="7">
         <v>1.2847222222222223E-3</v>
@@ -2934,7 +2951,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B93" s="7">
         <v>1.3321759259259259E-3</v>
@@ -2960,7 +2977,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B94" s="7">
         <v>1.195601851851852E-3</v>
@@ -2986,7 +3003,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B95" s="7">
         <v>1.2129629629629628E-3</v>
@@ -3012,7 +3029,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B96" s="7">
         <v>1.3321759259259259E-3</v>
